--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266014</v>
+        <v>124265906</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,47 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676620</v>
+        <v>676637</v>
       </c>
       <c r="R3" t="n">
-        <v>6616374</v>
+        <v>6616372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265482</v>
+        <v>124266014</v>
       </c>
       <c r="B4" t="n">
         <v>57666</v>
@@ -942,7 +933,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676455</v>
+        <v>676620</v>
       </c>
       <c r="R4" t="n">
-        <v>6616242</v>
+        <v>6616374</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265906</v>
+        <v>124265887</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676637</v>
+        <v>676623</v>
       </c>
       <c r="R5" t="n">
-        <v>6616372</v>
+        <v>6616364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1222,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266122</v>
+        <v>124265482</v>
       </c>
       <c r="B7" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,57 +1225,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676535</v>
+        <v>676455</v>
       </c>
       <c r="R7" t="n">
-        <v>6616305</v>
+        <v>6616242</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1306,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265887</v>
+        <v>124266122</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1340,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676623</v>
+        <v>676535</v>
       </c>
       <c r="R8" t="n">
-        <v>6616364</v>
+        <v>6616305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,6 +1424,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124265408</v>
+        <v>124265906</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676465</v>
+        <v>676637</v>
       </c>
       <c r="R2" t="n">
-        <v>6616238</v>
+        <v>6616372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265906</v>
+        <v>124265887</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676637</v>
+        <v>676623</v>
       </c>
       <c r="R3" t="n">
-        <v>6616372</v>
+        <v>6616364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124266014</v>
+        <v>124265408</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,9 +917,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676620</v>
+        <v>676465</v>
       </c>
       <c r="R4" t="n">
-        <v>6616374</v>
+        <v>6616238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265887</v>
+        <v>124266122</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,34 +1011,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676623</v>
+        <v>676535</v>
       </c>
       <c r="R5" t="n">
-        <v>6616364</v>
+        <v>6616305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,6 +1095,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1324,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266122</v>
+        <v>124266014</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,54 +1344,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676535</v>
+        <v>676620</v>
       </c>
       <c r="R8" t="n">
-        <v>6616305</v>
+        <v>6616374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1425,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124265906</v>
+        <v>124266122</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676637</v>
+        <v>676535</v>
       </c>
       <c r="R2" t="n">
-        <v>6616372</v>
+        <v>6616305</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265887</v>
+        <v>124265429</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +810,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676623</v>
+        <v>676461</v>
       </c>
       <c r="R3" t="n">
-        <v>6616364</v>
+        <v>6616241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265408</v>
+        <v>124265482</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -917,14 +939,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676465</v>
+        <v>676455</v>
       </c>
       <c r="R4" t="n">
-        <v>6616238</v>
+        <v>6616242</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124266122</v>
+        <v>124266014</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,54 +1024,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676535</v>
+        <v>676620</v>
       </c>
       <c r="R5" t="n">
-        <v>6616305</v>
+        <v>6616374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1105,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265429</v>
+        <v>124265887</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676461</v>
+        <v>676623</v>
       </c>
       <c r="R6" t="n">
-        <v>6616241</v>
+        <v>6616364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265482</v>
+        <v>124265408</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,9 +1263,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1270,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676455</v>
+        <v>676465</v>
       </c>
       <c r="R7" t="n">
-        <v>6616242</v>
+        <v>6616238</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266014</v>
+        <v>124265906</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,47 +1353,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676620</v>
+        <v>676637</v>
       </c>
       <c r="R8" t="n">
-        <v>6616374</v>
+        <v>6616372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124266122</v>
+        <v>124266014</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676535</v>
+        <v>676620</v>
       </c>
       <c r="R2" t="n">
-        <v>6616305</v>
+        <v>6616374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265429</v>
+        <v>124266122</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,39 +802,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676461</v>
+        <v>676535</v>
       </c>
       <c r="R3" t="n">
-        <v>6616241</v>
+        <v>6616305</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265482</v>
+        <v>124265906</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,50 +917,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676455</v>
+        <v>676637</v>
       </c>
       <c r="R4" t="n">
-        <v>6616242</v>
+        <v>6616372</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124266014</v>
+        <v>124265482</v>
       </c>
       <c r="B5" t="n">
         <v>57666</v>
@@ -1052,7 +1047,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676620</v>
+        <v>676455</v>
       </c>
       <c r="R5" t="n">
-        <v>6616374</v>
+        <v>6616242</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265887</v>
+        <v>124265429</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676623</v>
+        <v>676461</v>
       </c>
       <c r="R6" t="n">
-        <v>6616364</v>
+        <v>6616241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265408</v>
+        <v>124265887</v>
       </c>
       <c r="B7" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,48 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676465</v>
+        <v>676623</v>
       </c>
       <c r="R7" t="n">
-        <v>6616238</v>
+        <v>6616364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265906</v>
+        <v>124265408</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1343,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676637</v>
+        <v>676465</v>
       </c>
       <c r="R8" t="n">
-        <v>6616372</v>
+        <v>6616238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266122</v>
+        <v>124265906</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,50 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676535</v>
+        <v>676637</v>
       </c>
       <c r="R3" t="n">
-        <v>6616305</v>
+        <v>6616372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +870,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265906</v>
+        <v>124266122</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +904,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676637</v>
+        <v>676535</v>
       </c>
       <c r="R4" t="n">
-        <v>6616372</v>
+        <v>6616305</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124266014</v>
+        <v>124266122</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676620</v>
+        <v>676535</v>
       </c>
       <c r="R2" t="n">
-        <v>6616374</v>
+        <v>6616305</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265906</v>
+        <v>124265429</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -820,16 +828,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676637</v>
+        <v>676461</v>
       </c>
       <c r="R3" t="n">
-        <v>6616372</v>
+        <v>6616241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124266122</v>
+        <v>124265906</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,50 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676535</v>
+        <v>676637</v>
       </c>
       <c r="R4" t="n">
-        <v>6616305</v>
+        <v>6616372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265482</v>
+        <v>124265408</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,9 +1041,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676455</v>
+        <v>676465</v>
       </c>
       <c r="R5" t="n">
-        <v>6616242</v>
+        <v>6616238</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265429</v>
+        <v>124265482</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,31 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676461</v>
+        <v>676455</v>
       </c>
       <c r="R6" t="n">
-        <v>6616241</v>
+        <v>6616242</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265887</v>
+        <v>124266014</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,38 +1242,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676623</v>
+        <v>676620</v>
       </c>
       <c r="R7" t="n">
-        <v>6616364</v>
+        <v>6616374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265408</v>
+        <v>124265887</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,48 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676465</v>
+        <v>676623</v>
       </c>
       <c r="R8" t="n">
-        <v>6616238</v>
+        <v>6616364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124266122</v>
+        <v>124265887</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,50 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676535</v>
+        <v>676623</v>
       </c>
       <c r="R2" t="n">
-        <v>6616305</v>
+        <v>6616364</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265429</v>
+        <v>124265482</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +789,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676461</v>
+        <v>676455</v>
       </c>
       <c r="R3" t="n">
-        <v>6616241</v>
+        <v>6616242</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265906</v>
+        <v>124265429</v>
       </c>
       <c r="B4" t="n">
         <v>100279</v>
@@ -935,16 +922,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676637</v>
+        <v>676461</v>
       </c>
       <c r="R4" t="n">
-        <v>6616372</v>
+        <v>6616241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265408</v>
+        <v>124266014</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1007,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1041,14 +1033,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676465</v>
+        <v>676620</v>
       </c>
       <c r="R5" t="n">
-        <v>6616238</v>
+        <v>6616374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265482</v>
+        <v>124265906</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,50 +1118,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676455</v>
+        <v>676637</v>
       </c>
       <c r="R6" t="n">
-        <v>6616242</v>
+        <v>6616372</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266014</v>
+        <v>124266122</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,47 +1220,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676620</v>
+        <v>676535</v>
       </c>
       <c r="R7" t="n">
-        <v>6616374</v>
+        <v>6616305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265887</v>
+        <v>124265408</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1343,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676623</v>
+        <v>676465</v>
       </c>
       <c r="R8" t="n">
-        <v>6616364</v>
+        <v>6616238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124265887</v>
+        <v>124265482</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676623</v>
+        <v>676455</v>
       </c>
       <c r="R2" t="n">
-        <v>6616364</v>
+        <v>6616242</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265482</v>
+        <v>124266122</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +798,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676455</v>
+        <v>676535</v>
       </c>
       <c r="R3" t="n">
-        <v>6616242</v>
+        <v>6616305</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265429</v>
+        <v>124265408</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,27 +921,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676461</v>
+        <v>676465</v>
       </c>
       <c r="R4" t="n">
-        <v>6616241</v>
+        <v>6616238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1106,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265906</v>
+        <v>124265429</v>
       </c>
       <c r="B6" t="n">
         <v>100279</v>
@@ -1140,16 +1166,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676637</v>
+        <v>676461</v>
       </c>
       <c r="R6" t="n">
-        <v>6616372</v>
+        <v>6616241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266122</v>
+        <v>124265906</v>
       </c>
       <c r="B7" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,50 +1255,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676535</v>
+        <v>676637</v>
       </c>
       <c r="R7" t="n">
-        <v>6616305</v>
+        <v>6616372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1323,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265408</v>
+        <v>124265887</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,48 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676465</v>
+        <v>676623</v>
       </c>
       <c r="R8" t="n">
-        <v>6616238</v>
+        <v>6616364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124265482</v>
+        <v>124265887</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676455</v>
+        <v>676623</v>
       </c>
       <c r="R2" t="n">
-        <v>6616242</v>
+        <v>6616364</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1021,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124266014</v>
+        <v>124265429</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,35 +1024,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676620</v>
+        <v>676461</v>
       </c>
       <c r="R5" t="n">
-        <v>6616374</v>
+        <v>6616241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265429</v>
+        <v>124265482</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,31 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676461</v>
+        <v>676455</v>
       </c>
       <c r="R6" t="n">
-        <v>6616241</v>
+        <v>6616242</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1341,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265887</v>
+        <v>124266014</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,38 +1344,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676623</v>
+        <v>676620</v>
       </c>
       <c r="R8" t="n">
-        <v>6616364</v>
+        <v>6616374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124265887</v>
+        <v>124265906</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676623</v>
+        <v>676637</v>
       </c>
       <c r="R2" t="n">
-        <v>6616364</v>
+        <v>6616372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266122</v>
+        <v>124265887</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,50 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676535</v>
+        <v>676623</v>
       </c>
       <c r="R3" t="n">
-        <v>6616305</v>
+        <v>6616364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265408</v>
+        <v>124265482</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -934,14 +917,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676465</v>
+        <v>676455</v>
       </c>
       <c r="R4" t="n">
-        <v>6616238</v>
+        <v>6616242</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1119,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265482</v>
+        <v>124266122</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,50 +1109,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676455</v>
+        <v>676535</v>
       </c>
       <c r="R6" t="n">
-        <v>6616242</v>
+        <v>6616305</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,6 +1197,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265906</v>
+        <v>124266014</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,38 +1228,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676637</v>
+        <v>676620</v>
       </c>
       <c r="R7" t="n">
-        <v>6616372</v>
+        <v>6616374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266014</v>
+        <v>124265408</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,9 +1365,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676620</v>
+        <v>676465</v>
       </c>
       <c r="R8" t="n">
-        <v>6616374</v>
+        <v>6616238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124265906</v>
+        <v>124266014</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676637</v>
+        <v>676620</v>
       </c>
       <c r="R2" t="n">
-        <v>6616372</v>
+        <v>6616374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265887</v>
+        <v>124265482</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +798,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676623</v>
+        <v>676455</v>
       </c>
       <c r="R3" t="n">
-        <v>6616364</v>
+        <v>6616242</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265482</v>
+        <v>124265906</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,50 +909,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676455</v>
+        <v>676637</v>
       </c>
       <c r="R4" t="n">
-        <v>6616242</v>
+        <v>6616372</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265429</v>
+        <v>124265408</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,27 +1015,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676461</v>
+        <v>676465</v>
       </c>
       <c r="R5" t="n">
-        <v>6616241</v>
+        <v>6616238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266122</v>
+        <v>124265887</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,50 +1131,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676535</v>
+        <v>676623</v>
       </c>
       <c r="R6" t="n">
-        <v>6616305</v>
+        <v>6616364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1199,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266014</v>
+        <v>124265429</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,35 +1229,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676620</v>
+        <v>676461</v>
       </c>
       <c r="R7" t="n">
-        <v>6616374</v>
+        <v>6616241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1324,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265408</v>
+        <v>124266122</v>
       </c>
       <c r="B8" t="n">
         <v>105117</v>
@@ -1362,7 +1359,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1375,16 +1372,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676465</v>
+        <v>676535</v>
       </c>
       <c r="R8" t="n">
-        <v>6616238</v>
+        <v>6616305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,6 +1424,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18446-2025 artfynd.xlsx
+++ b/artfynd/A 18446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124266014</v>
+        <v>124265429</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676620</v>
+        <v>676461</v>
       </c>
       <c r="R2" t="n">
-        <v>6616374</v>
+        <v>6616241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265482</v>
+        <v>124265887</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676455</v>
+        <v>676623</v>
       </c>
       <c r="R3" t="n">
-        <v>6616242</v>
+        <v>6616364</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265906</v>
+        <v>124266122</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +900,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676637</v>
+        <v>676535</v>
       </c>
       <c r="R4" t="n">
-        <v>6616372</v>
+        <v>6616305</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265408</v>
+        <v>124265906</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,48 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676465</v>
+        <v>676637</v>
       </c>
       <c r="R5" t="n">
-        <v>6616238</v>
+        <v>6616372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265887</v>
+        <v>124265482</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,41 +1117,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676623</v>
+        <v>676455</v>
       </c>
       <c r="R6" t="n">
-        <v>6616364</v>
+        <v>6616242</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265429</v>
+        <v>124266014</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,31 +1228,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1262,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676461</v>
+        <v>676620</v>
       </c>
       <c r="R7" t="n">
-        <v>6616241</v>
+        <v>6616374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266122</v>
+        <v>124265408</v>
       </c>
       <c r="B8" t="n">
         <v>105117</v>
@@ -1359,7 +1362,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1372,18 +1375,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gubbkärret, Gubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676535</v>
+        <v>676465</v>
       </c>
       <c r="R8" t="n">
-        <v>6616305</v>
+        <v>6616238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1425,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
